--- a/output/metriques_desagregation.xlsx
+++ b/output/metriques_desagregation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/catherinehenri/PI4-THERMO-1/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C33890-8CBA-AB40-B664-E1A3C77119CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5632205A-3E47-9D4B-8212-64858AE3F2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="17720" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Métriques" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
   <si>
     <t>THERMO — Métriques de désagrégation (Climatisation)</t>
   </si>
@@ -74,6 +74,9 @@
     <t>FPR</t>
   </si>
   <si>
+    <t>Gap réel (%)</t>
+  </si>
+  <si>
     <t>TP</t>
   </si>
   <si>
@@ -95,6 +98,12 @@
     <t>2015-07-01</t>
   </si>
   <si>
+    <t>resultats_desagregation_3864_2015-08-01_7jours.csv</t>
+  </si>
+  <si>
+    <t>2015-08-01</t>
+  </si>
+  <si>
     <t>resultats_desagregation_3938_2016-07-01_7jours.csv</t>
   </si>
   <si>
@@ -104,27 +113,6 @@
     <t>2016-07-01</t>
   </si>
   <si>
-    <t>resultats_desagregation_4495_2018-07-01_7jours.csv</t>
-  </si>
-  <si>
-    <t>4495</t>
-  </si>
-  <si>
-    <t>2018-07-01</t>
-  </si>
-  <si>
-    <t>resultats_desagregation_4934_2015-07-01_7jours.csv</t>
-  </si>
-  <si>
-    <t>4934</t>
-  </si>
-  <si>
-    <t>resultats_desagregation_5938_2016-07-01_7jours.csv</t>
-  </si>
-  <si>
-    <t>5938</t>
-  </si>
-  <si>
     <t>resultats_desagregation_6377_2014-07-01_7jours.csv</t>
   </si>
   <si>
@@ -134,10 +122,10 @@
     <t>2014-07-01</t>
   </si>
   <si>
-    <t>resultats_desagregation_6547_2015-07-01_7jours.csv</t>
-  </si>
-  <si>
-    <t>6547</t>
+    <t>resultats_desagregation_6377_2014-08-01_7jours.csv</t>
+  </si>
+  <si>
+    <t>2014-08-01</t>
   </si>
   <si>
     <t>resultats_desagregation_7062_2014-07-01_7jours.csv</t>
@@ -146,37 +134,58 @@
     <t>7062</t>
   </si>
   <si>
+    <t>resultats_desagregation_7062_2014-08-01_7jours.csv</t>
+  </si>
+  <si>
     <t>resultats_desagregation_7114_2015-07-01_7jours.csv</t>
   </si>
   <si>
     <t>7114</t>
   </si>
   <si>
+    <t>resultats_desagregation_7114_2015-08-01_7jours.csv</t>
+  </si>
+  <si>
     <t>resultats_desagregation_8061_2016-07-01_7jours.csv</t>
   </si>
   <si>
     <t>8061</t>
   </si>
   <si>
-    <t>resultats_desagregation_8342_2018-07-01_7jours.csv</t>
+    <t>resultats_desagregation_8061_2016-08-01_7jours.csv</t>
+  </si>
+  <si>
+    <t>2016-08-01</t>
+  </si>
+  <si>
+    <t>resultats_desagregation_8342_2018-08-01_7jours.csv</t>
   </si>
   <si>
     <t>8342</t>
   </si>
   <si>
+    <t>2018-08-01</t>
+  </si>
+  <si>
     <t>resultats_desagregation_8574_2014-07-01_7jours.csv</t>
   </si>
   <si>
     <t>8574</t>
   </si>
   <si>
+    <t>resultats_desagregation_8574_2014-08-01_7jours.csv</t>
+  </si>
+  <si>
     <t>resultats_desagregation_8733_2014-07-01_7jours.csv</t>
   </si>
   <si>
     <t>8733</t>
   </si>
   <si>
-    <t>resultats_desagregation_9213_2014-07-01_7jours.csv</t>
+    <t>resultats_desagregation_8733_2014-08-01_7jours.csv</t>
+  </si>
+  <si>
+    <t>resultats_desagregation_9213_2014-08-01_7jours.csv</t>
   </si>
   <si>
     <t>9213</t>
@@ -186,6 +195,9 @@
   </si>
   <si>
     <t>9612</t>
+  </si>
+  <si>
+    <t>resultats_desagregation_9612_2014-08-01_7jours.csv</t>
   </si>
   <si>
     <t>MOYENNE</t>
@@ -623,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -631,14 +643,15 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="7" max="7" width="12" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="10" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="11" hidden="1" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
-    <col min="13" max="16" width="7" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="17" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -657,8 +670,9 @@
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
       <c r="P1" s="9"/>
-    </row>
-    <row r="2" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q1" s="9"/>
+    </row>
+    <row r="2" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -707,63 +721,67 @@
       <c r="P2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="28" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>672</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.23050000000000001</v>
+      </c>
+      <c r="F3" s="3">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.65349999999999997</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.55379999999999996</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.8286</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.77329999999999999</v>
+      </c>
+      <c r="L3" s="3">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3">
+        <v>29</v>
+      </c>
+      <c r="O3" s="3">
+        <v>626</v>
+      </c>
+      <c r="P3" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" s="3">
-        <v>672</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.20449999999999999</v>
-      </c>
-      <c r="F3" s="3">
-        <v>3.49E-2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.72929999999999995</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.44390000000000002</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="J3" s="3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0.80600000000000005</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>27</v>
-      </c>
-      <c r="N3" s="3">
-        <v>632</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -772,39 +790,44 @@
         <v>672</v>
       </c>
       <c r="E4" s="5">
-        <v>0.2041</v>
+        <v>0.48870000000000002</v>
       </c>
       <c r="F4" s="5">
-        <v>3.8699999999999998E-2</v>
+        <v>0.17549999999999999</v>
       </c>
       <c r="G4" s="5">
-        <v>26000000000</v>
+        <v>0.64670000000000005</v>
       </c>
       <c r="H4" s="5">
-        <v>26000000000</v>
-      </c>
-      <c r="I4" s="5"/>
+        <v>0.63839999999999997</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.57140000000000002</v>
+      </c>
       <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5"/>
+        <v>0.75790000000000002</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.65159999999999996</v>
+      </c>
       <c r="L4" s="5">
-        <v>5.9499999999999997E-2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="M4" s="5"/>
       <c r="N4" s="5">
-        <v>632</v>
+        <v>72</v>
       </c>
       <c r="O4" s="5">
-        <v>40</v>
+        <v>523</v>
       </c>
       <c r="P4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="28" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="28" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -818,16 +841,16 @@
         <v>672</v>
       </c>
       <c r="E5" s="3">
-        <v>0.1613</v>
+        <v>0.1125</v>
       </c>
       <c r="F5" s="3">
-        <v>4.7600000000000003E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G5" s="3">
-        <v>1684.2104999999999</v>
+        <v>14000000000</v>
       </c>
       <c r="H5" s="3">
-        <v>1684.1578999999999</v>
+        <v>14000000000</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
@@ -835,22 +858,23 @@
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3">
-        <v>9.2299999999999993E-2</v>
-      </c>
-      <c r="M5" s="3">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3">
         <v>0</v>
       </c>
-      <c r="N5" s="3">
-        <v>610</v>
-      </c>
       <c r="O5" s="3">
-        <v>62</v>
+        <v>646</v>
       </c>
       <c r="P5" s="3">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="28" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
@@ -858,312 +882,326 @@
         <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D6" s="5">
         <v>672</v>
       </c>
       <c r="E6" s="5">
-        <v>0.1482</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="F6" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>9.3899999999999997E-2</v>
       </c>
       <c r="G6" s="5">
-        <v>19500000000</v>
+        <v>0.73309999999999997</v>
       </c>
       <c r="H6" s="5">
-        <v>19500000000</v>
-      </c>
-      <c r="I6" s="5"/>
+        <v>1.0059</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.41070000000000001</v>
+      </c>
       <c r="J6" s="5">
+        <v>0.34849999999999998</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0.377</v>
+      </c>
+      <c r="L6" s="5">
+        <v>6.9800000000000001E-2</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5">
+        <v>23</v>
+      </c>
+      <c r="O6" s="5">
+        <v>573</v>
+      </c>
+      <c r="P6" s="5">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="3">
+        <v>672</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.245</v>
+      </c>
+      <c r="F7" s="3">
+        <v>7.3700000000000002E-2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.96440000000000003</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1.7052</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.1429</v>
+      </c>
+      <c r="J7" s="3">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="3">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
+        <v>4</v>
+      </c>
+      <c r="O7" s="3">
+        <v>596</v>
+      </c>
+      <c r="P7" s="3">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5">
+        <v>672</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.70450000000000002</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.26140000000000002</v>
+      </c>
+      <c r="G8" s="5">
+        <v>11.2256</v>
+      </c>
+      <c r="H8" s="5">
+        <v>11.984999999999999</v>
+      </c>
+      <c r="I8" s="5">
         <v>0</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5">
-        <v>5.21E-2</v>
-      </c>
-      <c r="M6" s="5">
+      <c r="J8" s="5">
         <v>0</v>
       </c>
-      <c r="N6" s="5">
-        <v>637</v>
-      </c>
-      <c r="O6" s="5">
-        <v>35</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="K8" s="5"/>
+      <c r="L8" s="5">
+        <v>0.18110000000000001</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="3">
-        <v>672</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.1173</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2.75E-2</v>
-      </c>
-      <c r="G7" s="3">
-        <v>2055.5556000000001</v>
-      </c>
-      <c r="H7" s="3">
-        <v>2056.5556000000001</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>5.5100000000000003E-2</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
-        <v>635</v>
-      </c>
-      <c r="O7" s="3">
-        <v>37</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="5">
-        <v>672</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0.3034</v>
-      </c>
-      <c r="F8" s="5">
-        <v>9.2399999999999996E-2</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.59760000000000002</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0.98919999999999997</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0.39290000000000003</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0.41510000000000002</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0.4037</v>
-      </c>
-      <c r="L8" s="5">
-        <v>5.0299999999999997E-2</v>
-      </c>
-      <c r="M8" s="5">
-        <v>22</v>
-      </c>
-      <c r="N8" s="5">
-        <v>585</v>
-      </c>
       <c r="O8" s="5">
-        <v>31</v>
+        <v>547</v>
       </c>
       <c r="P8" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3">
+        <v>672</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.45610000000000001</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.16650000000000001</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2.5785</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2.7342</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3">
+        <v>17</v>
+      </c>
+      <c r="O9" s="3">
+        <v>536</v>
+      </c>
+      <c r="P9" s="3">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3">
-        <v>672</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.19589999999999999</v>
-      </c>
-      <c r="F9" s="3">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2.1776</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1.1776</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.31669999999999998</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0.48099999999999998</v>
-      </c>
-      <c r="L9" s="3">
-        <v>6.2799999999999995E-2</v>
-      </c>
-      <c r="M9" s="3">
-        <v>19</v>
-      </c>
-      <c r="N9" s="3">
-        <v>612</v>
-      </c>
-      <c r="O9" s="3">
-        <v>41</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5">
+        <v>672</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.41020000000000001</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.1065</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.71150000000000002</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.72760000000000002</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.57889999999999997</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0.78569999999999995</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2.01E-2</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5">
+        <v>44</v>
+      </c>
+      <c r="O10" s="5">
+        <v>584</v>
+      </c>
+      <c r="P10" s="5">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="5">
-        <v>672</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0.62170000000000003</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0.1978</v>
-      </c>
-      <c r="G10" s="5">
-        <v>8.2230000000000008</v>
-      </c>
-      <c r="H10" s="5">
-        <v>9.0711999999999993</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5">
-        <v>0.1153</v>
-      </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
-        <v>591</v>
-      </c>
-      <c r="O10" s="5">
-        <v>77</v>
-      </c>
-      <c r="P10" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3">
+        <v>672</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.52290000000000003</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.1799</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.62660000000000005</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.64190000000000003</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.53029999999999999</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.89739999999999998</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3">
+        <v>70</v>
+      </c>
+      <c r="O11" s="3">
+        <v>532</v>
+      </c>
+      <c r="P11" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="3">
-        <v>672</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0.45119999999999999</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.1171</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0.38109999999999999</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.80010000000000003</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.38159999999999999</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.9355</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0.54210000000000003</v>
-      </c>
-      <c r="L11" s="3">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="M11" s="3">
-        <v>29</v>
-      </c>
-      <c r="N11" s="3">
-        <v>594</v>
-      </c>
-      <c r="O11" s="3">
-        <v>2</v>
-      </c>
-      <c r="P11" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D12" s="5">
         <v>672</v>
       </c>
       <c r="E12" s="5">
-        <v>5.4600000000000003E-2</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F12" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>3.3500000000000002E-2</v>
       </c>
       <c r="G12" s="5">
-        <v>4000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="H12" s="5">
-        <v>4000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
@@ -1171,320 +1209,533 @@
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5">
-        <v>1.1900000000000001E-2</v>
-      </c>
-      <c r="M12" s="5">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5">
         <v>0</v>
       </c>
-      <c r="N12" s="5">
-        <v>664</v>
-      </c>
       <c r="O12" s="5">
-        <v>8</v>
+        <v>627</v>
       </c>
       <c r="P12" s="5">
+        <v>45</v>
+      </c>
+      <c r="Q12" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3">
+        <v>672</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.21629999999999999</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.71579999999999999</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.64239999999999997</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.50680000000000003</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.66069999999999995</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.5736</v>
+      </c>
+      <c r="L13" s="3">
+        <v>7.22E-2</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3">
+        <v>74</v>
+      </c>
+      <c r="O13" s="3">
+        <v>488</v>
+      </c>
+      <c r="P13" s="3">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3">
-        <v>672</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0.1573</v>
-      </c>
-      <c r="F13" s="3">
-        <v>4.0800000000000003E-2</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1.2719</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0.89190000000000003</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K13" s="3">
-        <v>0.6804</v>
-      </c>
-      <c r="L13" s="3">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="M13" s="3">
+      <c r="C14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="5">
+        <v>672</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0.20979999999999999</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.873</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.36730000000000002</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.76619999999999999</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0.84379999999999999</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2.12E-2</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5">
+        <v>154</v>
+      </c>
+      <c r="O14" s="5">
+        <v>461</v>
+      </c>
+      <c r="P14" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="3">
+        <v>672</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.1108</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.46E-2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2357.1428999999998</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2358.1428999999998</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>639</v>
+      </c>
+      <c r="P15" s="3">
         <v>33</v>
       </c>
-      <c r="N13" s="3">
-        <v>608</v>
-      </c>
-      <c r="O13" s="3">
-        <v>27</v>
-      </c>
-      <c r="P13" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="5">
-        <v>672</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0.1002</v>
-      </c>
-      <c r="F14" s="5">
-        <v>2.01E-2</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1928.5714</v>
-      </c>
-      <c r="H14" s="5">
-        <v>1929.5714</v>
-      </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5">
+      <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5">
-        <v>4.02E-2</v>
-      </c>
-      <c r="M14" s="5">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5">
-        <v>645</v>
-      </c>
-      <c r="O14" s="5">
-        <v>27</v>
-      </c>
-      <c r="P14" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="3">
-        <v>672</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.64039999999999997</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.35520000000000002</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.40679999999999999</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.84819999999999995</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0.25180000000000002</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0.85189999999999999</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0.38869999999999999</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3.0200000000000001E-2</v>
-      </c>
-      <c r="M15" s="3">
-        <v>69</v>
-      </c>
-      <c r="N15" s="3">
-        <v>386</v>
-      </c>
-      <c r="O15" s="3">
-        <v>12</v>
-      </c>
-      <c r="P15" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5">
+        <v>672</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.27750000000000002</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0.10589999999999999</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1.1918</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1.1011</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.63290000000000002</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0.45450000000000002</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0.52910000000000001</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0.1012</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5">
+        <v>50</v>
+      </c>
+      <c r="O16" s="5">
+        <v>533</v>
+      </c>
+      <c r="P16" s="5">
+        <v>60</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="5">
-        <v>672</v>
-      </c>
-      <c r="E16" s="5">
-        <v>0.42220000000000002</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0.18010000000000001</v>
-      </c>
-      <c r="G16" s="5">
-        <v>1.1054999999999999</v>
-      </c>
-      <c r="H16" s="5">
-        <v>1.0660000000000001</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0.50680000000000003</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0.70479999999999998</v>
-      </c>
-      <c r="K16" s="5">
-        <v>0.58960000000000001</v>
-      </c>
-      <c r="L16" s="5">
-        <v>5.8900000000000001E-2</v>
-      </c>
-      <c r="M16" s="5">
-        <v>74</v>
-      </c>
-      <c r="N16" s="5">
-        <v>495</v>
-      </c>
-      <c r="O16" s="5">
+      <c r="C17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="3">
+        <v>672</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.63109999999999999</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.3674</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.58630000000000004</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.87719999999999998</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.37590000000000001</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.66879999999999995</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.48130000000000001</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.12809999999999999</v>
+      </c>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3">
+        <v>103</v>
+      </c>
+      <c r="O17" s="3">
+        <v>347</v>
+      </c>
+      <c r="P17" s="3">
+        <v>51</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="5">
+        <v>672</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0.3291</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.76680000000000004</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0.78139999999999998</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0.79169999999999996</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0.6129</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0.1087</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5">
+        <v>152</v>
+      </c>
+      <c r="O18" s="5">
+        <v>328</v>
+      </c>
+      <c r="P18" s="5">
+        <v>40</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="3">
+        <v>672</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.35389999999999999</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.15290000000000001</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.84670000000000001</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.32679999999999998</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.61729999999999996</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.4274</v>
+      </c>
+      <c r="L19" s="3">
+        <v>5.9700000000000003E-2</v>
+      </c>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3">
+        <v>50</v>
+      </c>
+      <c r="O19" s="3">
+        <v>488</v>
+      </c>
+      <c r="P19" s="3">
         <v>31</v>
       </c>
-      <c r="P16" s="5">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="3">
-        <v>672</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0.49340000000000001</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.64359999999999995</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.31509999999999999</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0.98680000000000001</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0.47770000000000001</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2.3E-3</v>
-      </c>
-      <c r="M17" s="3">
-        <v>75</v>
-      </c>
-      <c r="N17" s="3">
-        <v>433</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1</v>
-      </c>
-      <c r="P17" s="3">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="7" t="s">
+      <c r="Q19" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="7">
-        <v>672</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.2908</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0.1004</v>
-      </c>
-      <c r="G18" s="7">
-        <v>3300000378.9148998</v>
-      </c>
-      <c r="H18" s="7">
-        <v>3300000379.0525999</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0.49059999999999998</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0.3841</v>
-      </c>
-      <c r="K18" s="7">
-        <v>0.54620000000000002</v>
-      </c>
-      <c r="L18" s="7">
-        <v>4.5100000000000001E-2</v>
-      </c>
-      <c r="M18" s="7">
-        <v>23.2</v>
-      </c>
-      <c r="N18" s="7">
-        <v>583.93330000000003</v>
-      </c>
-      <c r="O18" s="7">
-        <v>28.7333</v>
-      </c>
-      <c r="P18" s="7">
-        <v>36.133299999999998</v>
+      <c r="B20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="5">
+        <v>672</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.57589999999999997</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.25459999999999999</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.50060000000000004</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0.437</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0.94550000000000001</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0.59770000000000001</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1.38E-2</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5">
+        <v>104</v>
+      </c>
+      <c r="O20" s="5">
+        <v>428</v>
+      </c>
+      <c r="P20" s="5">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="3">
+        <v>672</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.51139999999999997</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.2195</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.57169999999999999</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.55649999999999999</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.97709999999999997</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.67190000000000005</v>
+      </c>
+      <c r="L21" s="3">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3">
+        <v>128</v>
+      </c>
+      <c r="O21" s="3">
+        <v>419</v>
+      </c>
+      <c r="P21" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="7">
+        <v>672</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.4047</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0.1598</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1921052756.8949001</v>
+      </c>
+      <c r="H22" s="7">
+        <v>1921052757.0486</v>
+      </c>
+      <c r="I22" s="7">
+        <v>0.4718</v>
+      </c>
+      <c r="J22" s="7">
+        <v>0.52049999999999996</v>
+      </c>
+      <c r="K22" s="7">
+        <v>0.54630000000000001</v>
+      </c>
+      <c r="L22" s="7">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="7">
+        <v>56.526299999999999</v>
+      </c>
+      <c r="O22" s="7">
+        <v>522.15790000000004</v>
+      </c>
+      <c r="P22" s="7">
+        <v>37.263199999999998</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>56.052599999999998</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/metriques_desagregation.xlsx
+++ b/output/metriques_desagregation.xlsx
@@ -161,19 +161,19 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,23 +541,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
@@ -565,7 +565,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>THERMO — Récapitulatif des métriques (tous clients)</t>
+          <t>THERMO - Récapitulatif des métriques (tous clients)</t>
         </is>
       </c>
     </row>
@@ -1313,10 +1313,911 @@
         <v>1288.9091</v>
       </c>
     </row>
+    <row r="15" ht="10" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Moyenne tous clients - Par saison  (11 clients)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>N pas</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>RMSE (kW)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>MAE (kW)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Energy Frac</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Norm Err</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>FPR</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Hiver</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>5568</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1272727292.0644</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1272727292.6444</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>5533.5455</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>12.6364</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>21.0909</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Printemps</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>6536.7273</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>1045454545.8985</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1045454546.1525</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>78.0909</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>6192.2727</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>59.5455</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>206.8182</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Été</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>7121.4545</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1.0572</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.5357</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>601.9091</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>5554</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>306</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>659.5454999999999</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Automne</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>5829.8182</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1.0337</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1.0602</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.6334</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.5326</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>411.8182</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>4807.7273</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>208.8182</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>401.4545</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Moyenne tous clients - Par mois  (11 clients)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>N pas</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>RMSE (kW)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>MAE (kW)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Energy Frac</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Norm Err</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>FPR</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>2272</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1055555564.0343</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1055555564.4663</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>2255.7778</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>8.222200000000001</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Fév</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1322.6667</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>8.6478</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>9.088100000000001</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>1316.2222</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>3.4444</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>2365.0909</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>772727278.2714</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>772727278.6059999</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>15.8182</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>2291.5455</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>13.2727</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>44.4545</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Avr</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>1867.6364</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>409090922.351</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>409090922.7065</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>11.8182</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>1792.7273</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>15.0909</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>2534.4</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0.6108</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.4217</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>2318.8</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>1877.3333</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>111111155.1995</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>111111155.5218</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>38.3333</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>1668</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>57.4444</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>113.5556</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>2539.6364</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>1.4368</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1.3484</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.7040999999999999</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>233.7273</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>1955.8182</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>122.1818</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>227.9091</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Aoû</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>3045.8182</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>1.0361</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1.0367</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.5127</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.5417</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>336.8182</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>2233.4545</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>136.8182</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>338.7273</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>2487.2727</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1.6959</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.6778</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.7315</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>315.2727</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>1794.8182</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>272.1818</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>2083.2</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1.1612</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1.2592</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>1788</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>1448.7273</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>2454545777.9946</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>2454545778.3535</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>11.0909</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>1387.4545</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>29.5455</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>20.6364</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Déc</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>2626.9091</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>454545472.5546</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>454545473.1224</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>2611</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>3.0909</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>12.0909</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A23:N23"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A16:N16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1350,12 +2251,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 8733 — ANNEE 2014</t>
+          <t>Client 8733 - ANNEE 2014</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (30624 pas)</t>
         </is>
@@ -1480,7 +2381,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -1605,7 +2506,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -1697,7 +2598,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -1743,7 +2644,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -1868,7 +2769,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -1960,7 +2861,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -2052,7 +2953,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -2144,7 +3045,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -2236,7 +3137,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -2320,12 +3221,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 9213 — ANNEE 2014</t>
+          <t>Client 9213 - ANNEE 2014</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (16800 pas)</t>
         </is>
@@ -2450,7 +3351,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -2551,7 +3452,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -2559,7 +3460,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -2579,7 +3480,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -2601,7 +3502,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
@@ -2609,7 +3510,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
@@ -2675,7 +3576,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -2721,7 +3622,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -2822,7 +3723,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
@@ -2830,7 +3731,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -2850,7 +3751,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -2872,17 +3773,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -2924,7 +3825,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
@@ -2932,7 +3833,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
@@ -2952,7 +3853,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -2974,17 +3875,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
@@ -3050,7 +3951,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -3142,7 +4043,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -3210,7 +4111,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
@@ -3218,7 +4119,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="6" t="n">
@@ -3238,7 +4139,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -3260,17 +4161,17 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
@@ -3328,12 +4229,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 9612 — ANNEE 2014</t>
+          <t>Client 9612 - ANNEE 2014</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (25248 pas)</t>
         </is>
@@ -3458,7 +4359,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -3583,7 +4484,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -3675,7 +4576,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -3721,7 +4622,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -3846,7 +4747,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -3938,7 +4839,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -4030,7 +4931,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -4122,7 +5023,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -4214,7 +5115,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -4298,12 +5199,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 3864 — ANNEE 2015</t>
+          <t>Client 3864 - ANNEE 2015</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (20832 pas)</t>
         </is>
@@ -4428,7 +5329,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -4529,7 +5430,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -4537,7 +5438,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -4557,7 +5458,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -4649,7 +5550,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -4695,7 +5596,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -4796,17 +5697,17 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -4826,7 +5727,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -4848,17 +5749,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -4924,7 +5825,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -4992,17 +5893,17 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
@@ -5022,7 +5923,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -5114,7 +6015,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -5206,7 +6107,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -5274,17 +6175,17 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
@@ -5304,7 +6205,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -5326,7 +6227,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
@@ -5334,7 +6235,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
@@ -5392,12 +6293,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 3938 — ANNEE 2016</t>
+          <t>Client 3938 - ANNEE 2016</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (17472 pas)</t>
         </is>
@@ -5522,7 +6423,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -5623,7 +6524,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -5631,7 +6532,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -5651,7 +6552,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -5673,17 +6574,17 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
@@ -5749,7 +6650,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -5795,7 +6696,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -5896,17 +6797,17 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -5926,7 +6827,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -5948,17 +6849,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -6000,17 +6901,17 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
@@ -6030,7 +6931,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -6052,17 +6953,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
@@ -6104,17 +7005,17 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
@@ -6134,7 +7035,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -6226,7 +7127,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -6318,7 +7219,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -6386,7 +7287,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -6394,7 +7295,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
@@ -6414,7 +7315,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -6436,7 +7337,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
@@ -6444,7 +7345,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
@@ -6502,12 +7403,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 6377 — ANNEE 2014</t>
+          <t>Client 6377 - ANNEE 2014</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (15456 pas)</t>
         </is>
@@ -6632,7 +7533,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -6733,7 +7634,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -6741,7 +7642,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -6761,7 +7662,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -6853,7 +7754,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -6899,7 +7800,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -7000,7 +7901,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
@@ -7008,7 +7909,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -7028,7 +7929,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -7050,17 +7951,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -7102,17 +8003,17 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
@@ -7132,7 +8033,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -7154,7 +8055,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
@@ -7162,7 +8063,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
@@ -7228,7 +8129,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
@@ -7320,7 +8221,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
@@ -7388,7 +8289,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
@@ -7396,7 +8297,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="6" t="n">
@@ -7416,7 +8317,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -7438,7 +8339,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
@@ -7446,7 +8347,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
@@ -7504,12 +8405,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 7062 — ANNEE 2014</t>
+          <t>Client 7062 - ANNEE 2014</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (33600 pas)</t>
         </is>
@@ -7634,7 +8535,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -7741,7 +8642,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -7761,7 +8662,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -7853,7 +8754,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -7899,7 +8800,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -8006,7 +8907,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -8026,7 +8927,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -8051,12 +8952,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -8122,7 +9023,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -8214,7 +9115,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -8306,7 +9207,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -8398,7 +9299,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -8490,7 +9391,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -8518,7 +9419,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
@@ -8576,12 +9477,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 7114 — ANNEE 2015</t>
+          <t>Client 7114 - ANNEE 2015</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (25536 pas)</t>
         </is>
@@ -8706,7 +9607,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -8807,7 +9708,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -8815,7 +9716,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -8835,7 +9736,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -8927,7 +9828,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -8973,7 +9874,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -9074,7 +9975,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
@@ -9082,7 +9983,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -9102,7 +10003,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -9124,17 +10025,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -9200,7 +10101,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -9292,7 +10193,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -9384,7 +10285,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -9476,7 +10377,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -9544,7 +10445,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -9552,7 +10453,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
@@ -9572,7 +10473,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -9594,7 +10495,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
@@ -9602,7 +10503,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
@@ -9660,12 +10561,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 8061 — ANNEE 2016</t>
+          <t>Client 8061 - ANNEE 2016</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (29568 pas)</t>
         </is>
@@ -9790,7 +10691,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -9891,17 +10792,17 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -9921,7 +10822,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -9943,7 +10844,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
@@ -9951,7 +10852,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
@@ -10017,7 +10918,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -10063,7 +10964,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -10164,17 +11065,17 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -10194,7 +11095,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -10216,17 +11117,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -10268,7 +11169,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
@@ -10276,7 +11177,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
@@ -10296,7 +11197,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -10318,7 +11219,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
@@ -10326,7 +11227,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
@@ -10368,17 +11269,17 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
@@ -10398,7 +11299,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -10490,7 +11391,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -10582,7 +11483,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -10650,7 +11551,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -10658,7 +11559,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
@@ -10678,7 +11579,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -10700,17 +11601,17 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
@@ -10768,12 +11669,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 8342 — ANNEE 2018</t>
+          <t>Client 8342 - ANNEE 2018</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (24192 pas)</t>
         </is>
@@ -10898,7 +11799,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -10999,7 +11900,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -11007,7 +11908,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -11027,7 +11928,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -11049,7 +11950,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
@@ -11057,7 +11958,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
@@ -11123,7 +12024,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -11169,7 +12070,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -11270,7 +12171,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
@@ -11278,7 +12179,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -11298,7 +12199,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -11320,17 +12221,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -11372,7 +12273,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
@@ -11380,7 +12281,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
@@ -11400,7 +12301,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -11422,7 +12323,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
@@ -11430,7 +12331,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
@@ -11472,17 +12373,17 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
@@ -11502,7 +12403,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -11524,7 +12425,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
@@ -11532,7 +12433,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
@@ -11598,7 +12499,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -11690,7 +12591,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -11758,7 +12659,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -11766,7 +12667,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
@@ -11786,7 +12687,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -11808,7 +12709,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
@@ -11816,7 +12717,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
@@ -11874,12 +12775,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Client 8574 — ANNEE 2014</t>
+          <t>Client 8574 - ANNEE 2014</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Métriques globales (36288 pas)</t>
         </is>
@@ -12004,7 +12905,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Par saison</t>
         </is>
@@ -12105,7 +13006,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -12113,7 +13014,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -12133,7 +13034,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Printemps</t>
         </is>
@@ -12225,7 +13126,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Automne</t>
         </is>
@@ -12271,7 +13172,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Par mois</t>
         </is>
@@ -12372,7 +13273,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
@@ -12380,7 +13281,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
@@ -12400,7 +13301,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fév</t>
         </is>
@@ -12422,7 +13323,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
@@ -12430,7 +13331,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -12472,7 +13373,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
@@ -12480,7 +13381,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
@@ -12500,7 +13401,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avr</t>
         </is>
@@ -12522,7 +13423,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
@@ -12530,7 +13431,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
@@ -12596,7 +13497,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
@@ -12618,7 +13519,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
@@ -12626,7 +13527,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
@@ -12692,7 +13593,7 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Aoû</t>
         </is>
@@ -12784,7 +13685,7 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
@@ -12852,7 +13753,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
@@ -12860,7 +13761,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
@@ -12880,7 +13781,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Déc</t>
         </is>
@@ -12902,7 +13803,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
@@ -12910,7 +13811,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
